--- a/data/temp/temp_スキルシート.xlsx
+++ b/data/temp/temp_スキルシート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D94EB8-CBA0-4582-B4F8-C66D88C46C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8ACD850-4065-4F9A-B813-266A14083AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>勤務先</t>
     <rPh sb="0" eb="3">
@@ -162,51 +162,83 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>ｙｙｙｙ/ｍｍ/ｄｄ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;勤務先&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;案件名&gt;</t>
+    <rPh sb="1" eb="4">
+      <t>アンケンメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;期間&gt;</t>
+    <rPh sb="1" eb="3">
+      <t>キカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>【担当プロジェクト概要】
-ZZZ
+&lt;担当プロジェクト概要&gt;
 【業務内容】
-・ZZZ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>yyyy年mm月
-から
-yyyy年mm月
-までの
-ZZヶ月間</t>
+&lt;業務内容&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>【環境】
-ZZZ
-ZZZ
+&lt;環境&gt;
 【言語】
-ZZZ
-ZZZ
+&lt;言語&gt;
 【ツール】
-ZZZ
-ZZZ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メンバー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チーム人数：Z人
-規模：Z規模</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>〇</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ｙｙｙｙ/ｍｍ/ｄｄ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ZZZ</t>
+&lt;ツール&gt;</t>
+    <rPh sb="6" eb="8">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ゲンゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;規模・人数&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;要件定義&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;基本設計&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;詳細設計&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;実装&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;単テスト&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;結テスト&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;保守運用&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;役割・役職&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -402,44 +434,44 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,17 +771,17 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" ht="18.5" customHeight="1">
       <c r="A2" s="8" t="s">
@@ -783,124 +815,124 @@
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="19"/>
+      <c r="B4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="18.5" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="19"/>
+      <c r="B5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="13"/>
       <c r="D5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" spans="1:11" ht="18.5" customHeight="1">
-      <c r="A6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
+      <c r="B6" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
     </row>
     <row r="7" spans="1:11" ht="18.5" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:11" ht="18.5" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="11" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" ht="131" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:11" ht="18" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="11" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
     </row>
     <row r="11" spans="1:11" ht="25" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="6" t="s">
         <v>3</v>
       </c>
@@ -924,19 +956,31 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="23.5" customHeight="1">
-      <c r="A12" s="22"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="H12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+        <v>25</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
       <c r="A13" s="10"/>
@@ -953,6 +997,8 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="H1:K1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="E5:K5"/>
@@ -963,8 +1009,6 @@
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="E9:K9"/>
     <mergeCell ref="E10:K10"/>
-    <mergeCell ref="H1:K1"/>
-    <mergeCell ref="E1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
